--- a/outputs/evaluation/architecture/design/v4/CF_M01/run_2/CF_M01_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/design/v4/CF_M01/run_2/CF_M01_arch_eval.xlsx
@@ -508,6 +508,8 @@
         <v>0.8208</v>
       </c>
     </row>
+    <row r="5"/>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -590,7 +592,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>0.9091</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1213,7 +1215,6 @@
       <c r="D2" t="n">
         <v>0.7642</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1234,7 +1235,6 @@
           <t>['AU_07', 'AU_11']</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_30</t>
@@ -1245,7 +1245,6 @@
           <t>core, database</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1264,7 +1263,6 @@
           <t>CF_M01_AU11, CF_M01_AU15, CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M01_AU37</t>
@@ -1295,7 +1293,6 @@
       <c r="D3" t="n">
         <v>0.7871</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1316,7 +1313,6 @@
           <t>['AU_10', 'AU_11', 'AU_14']</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_32</t>
@@ -1327,7 +1323,6 @@
           <t>web socket, database, data lake</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1346,7 +1341,6 @@
           <t>CF_M01_AU27, CF_M01_AU13</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M01_AU28</t>
@@ -1402,13 +1396,11 @@
           <t>['AU_11']</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>AU_13</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>AWS RDS</t>
@@ -1432,13 +1424,11 @@
           <t>CF_M01_AU15</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M01_AU35</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1459,7 +1449,6 @@
       <c r="D5" t="n">
         <v>0.8089</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1480,7 +1469,6 @@
           <t>['AU_07', 'AU_14']</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>AU_34</t>
@@ -1491,7 +1479,6 @@
           <t>core, data lake</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1510,7 +1497,6 @@
           <t>CF_M01_AU12, CF_M01_AU16, CF_M01_AU15</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M01_AU36</t>
@@ -1541,7 +1527,6 @@
       <c r="D6" t="n">
         <v>0.8135</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1562,7 +1547,6 @@
           <t>['AU_10', 'AU_26']</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>AU_29</t>
@@ -1573,7 +1557,6 @@
           <t>web socket, player</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1592,7 +1575,6 @@
           <t>CF_M01_AU27, CF_M01_AU14</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M01_AU29</t>
@@ -1623,7 +1605,6 @@
       <c r="D7" t="n">
         <v>0.8284</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1644,7 +1625,6 @@
           <t>['AU_06', 'AU_07', 'AU_08']</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_28</t>
@@ -1655,7 +1635,6 @@
           <t>api gateway, core, analytical module</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1674,7 +1653,6 @@
           <t>CF_M01_AU10, CF_M01_AU11, CF_M01_AU12</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M01_AU26</t>
@@ -1730,13 +1708,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>AU_07</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Core Service</t>
@@ -1760,13 +1736,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M01_AU11</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1812,13 +1786,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_11</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>SQL database</t>
@@ -1842,13 +1814,11 @@
           <t>CF_M01_AU07</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M01_AU15</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1869,7 +1839,6 @@
       <c r="D10" t="n">
         <v>0.9227</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1890,7 +1859,6 @@
           <t>['AU_03', 'AU_06']</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_27</t>
@@ -1901,7 +1869,6 @@
           <t>presentation layer, api gateway</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1920,7 +1887,6 @@
           <t>CF_M01_AU05, CF_M01_AU10</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M01_AU25</t>
@@ -1971,7 +1937,6 @@
           <t>43</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>Architectural Pattern</t>
@@ -1982,7 +1947,6 @@
           <t>P_03</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>API Gateway Service</t>
@@ -2006,13 +1970,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M01_AU10</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2058,13 +2020,11 @@
           <t>['AU_14']</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_16</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Amazon DynamoDB</t>
@@ -2088,13 +2048,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M01_AU18</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2140,13 +2098,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>AU_08</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Analytical module</t>
@@ -2170,13 +2126,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M01_AU12</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2222,13 +2176,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>AU_06</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>API Gateway</t>
@@ -2252,13 +2204,11 @@
           <t>CF_M01_P03</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M01_P04</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2304,13 +2254,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Api Player</t>
@@ -2334,13 +2282,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M01_AU13</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2386,13 +2332,11 @@
           <t>['AU_11']</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>AU_12</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>MySQL</t>
@@ -2416,13 +2360,11 @@
           <t>CF_M01_AU15</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CF_M01_AU32</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2463,14 +2405,11 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>AU_26</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Player</t>
@@ -2489,14 +2428,11 @@
       <c r="P17" t="n">
         <v>8</v>
       </c>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CF_M01_AU27</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2542,13 +2478,11 @@
           <t>['AU_08']</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>AU_20</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Amazon Athena</t>
@@ -2572,13 +2506,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>CF_M01_AU20</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2619,14 +2551,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>AU_03</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Presentation Layer</t>
@@ -2650,13 +2579,11 @@
           <t>CF_M01_P02</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>CF_M01_AU05</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2702,13 +2629,11 @@
           <t>['AU_27']</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>AU_24</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>HTTP</t>
@@ -2732,13 +2657,11 @@
           <t>CF_M01_AU24, CF_M01_AU25</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>CF_M01_AU03</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2784,13 +2707,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>AU_17</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>NestJS</t>
@@ -2814,13 +2735,11 @@
           <t>CF_M01_AU02</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>CF_M01_AU33</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2861,14 +2780,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Client</t>
@@ -2892,13 +2808,11 @@
           <t>CF_M01_P01</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>CF_M01_AU01</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2944,13 +2858,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>AU_10</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Web Socket</t>
@@ -2974,13 +2886,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>CF_M01_AU14</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3026,13 +2936,11 @@
           <t>['AU_14']</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>AU_15</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>Amazon S3</t>
@@ -3056,13 +2964,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>CF_M01_AU17</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3108,13 +3014,11 @@
           <t>['AU_08']</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>AU_21</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>AWS Glue</t>
@@ -3138,13 +3042,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>CF_M01_AU21</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3185,14 +3087,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>AU_04</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Business Layer</t>
@@ -3216,13 +3115,11 @@
           <t>CF_M01_P02</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3263,7 +3160,6 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>Architectural Pattern</t>
@@ -3274,7 +3170,6 @@
           <t>P_02</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>Three Layers</t>
@@ -3298,13 +3193,11 @@
           <t>CF_M01_P01</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
           <t>CF_M01_P02</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3345,14 +3238,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>AU_02</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>Server</t>
@@ -3376,13 +3266,11 @@
           <t>CF_M01_P01</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
           <t>CF_M01_AU02</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3428,13 +3316,11 @@
           <t>['AU_08']</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>AU_22</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>Kinesis Data Streams</t>
@@ -3460,13 +3346,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
           <t>CF_M01_AU22</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3507,7 +3391,6 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>Architectural Pattern</t>
@@ -3518,7 +3401,6 @@
           <t>P_01</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>Client-Server</t>
@@ -3537,14 +3419,11 @@
       <c r="P30" t="n">
         <v>41</v>
       </c>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
           <t>CF_M01_P01</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3590,13 +3469,11 @@
           <t>['AU_17']</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>AU_18</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>TypeScript</t>
@@ -3620,13 +3497,11 @@
           <t>CF_M01_AU33</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
           <t>CF_M01_AU34</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3667,14 +3542,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>AU_05</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>Data Layer</t>
@@ -3698,13 +3570,11 @@
           <t>CF_M01_P02</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
           <t>CF_M01_AU07</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3750,13 +3620,11 @@
           <t>['AU_08']</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>AU_23</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
           <t>Kinesis Data Firehose</t>
@@ -3780,13 +3648,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
           <t>CF_M01_AU23</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3832,13 +3698,11 @@
           <t>['AU_28']</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>AU_25</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
           <t>TCP</t>
@@ -3862,13 +3726,11 @@
           <t>CF_M01_AU26</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
           <t>CF_M01_AU31</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3942,7 +3804,6 @@
           <t>Data Lake</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>The objective of these services is to form a data lake where all the history is stored to be able to process them in the analytical module.</t>
@@ -3978,7 +3839,6 @@
           <t>AWS</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Cloud services used for infrastructure.</t>
@@ -4009,7 +3869,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>analytical module, database</t>
@@ -4045,7 +3904,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>analytical module, data lake</t>
@@ -4137,7 +3995,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>client, server</t>
@@ -4153,7 +4010,6 @@
           <t>AU_27</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>0.8191000000000001</v>
       </c>
@@ -4174,7 +4030,6 @@
           <t>REST</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
@@ -4210,7 +4065,6 @@
           <t>Web platform interface</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
@@ -4246,7 +4100,6 @@
           <t>Waapiti Mobile Platform</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
@@ -4277,7 +4130,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>presentation layer, business layer</t>
@@ -4318,7 +4170,6 @@
           <t>AWS cloud services set</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. […] The objective of these services is to form a data lake where all the historical data is stored in order to process them in the analytical module.</t>
@@ -4354,7 +4205,6 @@
           <t>Service-oriented</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Both the business layer and the data layer are divided into several different services</t>
